--- a/sources/jack2_step3.xlsx
+++ b/sources/jack2_step3.xlsx
@@ -868,6 +868,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
@@ -915,6 +920,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
@@ -957,6 +967,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
@@ -997,6 +1012,11 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5337,6 +5357,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
@@ -5364,6 +5389,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
@@ -5391,6 +5421,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
@@ -5416,6 +5451,11 @@
       <c r="I105" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">

--- a/sources/jack2_step3.xlsx
+++ b/sources/jack2_step3.xlsx
@@ -4730,9 +4730,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <f>~3+4</f>
-        <v/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4782,6 +4783,11 @@
       <c r="O87" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4824,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4861,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4918,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
